--- a/artfynd/A 34263-2025 artfynd.xlsx
+++ b/artfynd/A 34263-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AY10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,53 +675,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>2454432</v>
+        <v>69187278</v>
       </c>
       <c r="B2" t="n">
-        <v>96236</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80703</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220093</v>
+        <v>226</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Skuggorangelav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Caloplaca lucifuga</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Châtel.</t>
+          <t>G.Thor</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Sålleryd 150 m OSO, Ög</t>
+          <t>Sålleryd, Ög</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>491413.8286807284</v>
+        <v>491213</v>
       </c>
       <c r="R2" t="n">
-        <v>6458615.810412084</v>
+        <v>6458718</v>
       </c>
       <c r="S2" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,22 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2002-07-20</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2017-11-15</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2002-07-20</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2017-11-15</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -771,74 +756,68 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
-      </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>Mossekant</t>
-        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Jörgen Josefsson</t>
+          <t>Tomas Fasth</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Jörgen Josefsson</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr"/>
+          <t>Tomas Fasth</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>Ödeshög naturvårdsprogram uppdatering</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>6999611</v>
+        <v>148302</v>
       </c>
       <c r="B3" t="n">
-        <v>103164</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83304</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221137</v>
+        <v>311</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Majviva</t>
+          <t>Brun nållav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Primula farinosa</t>
+          <t>Chaenotheca phaeocephala</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Turner) Th.Fr.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Sålleryd, Ög</t>
+          <t>(08E2i14), Ög</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>491186.3007786747</v>
+        <v>491224</v>
       </c>
       <c r="R3" t="n">
-        <v>6458678.382028894</v>
+        <v>6458721</v>
       </c>
       <c r="S3" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -862,27 +841,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>1978-05-20</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>1996-06-29</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>1999-10-07</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>1996-06-29</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Medobservatör: Erik Genberg</t>
+          <t>080428141 / CHA PHAE / Enstaka-sparsam (1)  / OBJ.AREA:0,1 ha</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -893,73 +862,78 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>Grova ädellövträd /</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>Gammal grov ek</t>
+        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Stefan Karlsson</t>
+          <t>Niklas Lönnell</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Stefan Karlsson</t>
+          <t>Ulf Kleist</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>Äldre fynd i Östergötlands flora</t>
+          <t>Skogsstyrelsens Nyckelbiotopsinventering (NBI)</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>87496103</v>
+        <v>69187281</v>
       </c>
       <c r="B4" t="n">
-        <v>101691</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83304</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220164</v>
+        <v>311</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Solvända</t>
+          <t>Brun nållav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Helianthemum nummularium</t>
+          <t>Chaenotheca phaeocephala</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Mill.</t>
+          <t>(Turner) Th.Fr.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Ängsbacke V Sållerydsfuktängen, Ög</t>
+          <t>Sålleryd, Ög</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>491086.5284495048</v>
+        <v>491243</v>
       </c>
       <c r="R4" t="n">
-        <v>6458836.9344129</v>
+        <v>6458709</v>
       </c>
       <c r="S4" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -983,27 +957,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>1975-06-07</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2017-11-15</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>1975-06-07</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Äldre uppgifter om Östergötlands flora. Referens: Hallberg, H. Peter 1975. Sektion 67, St Åby och Rök. Manuskript i PÖF Arkiv, Norrköping, 15+2 s. Inlagda i Artportalen av Tommy Tyrberg.</t>
+          <t>2017-11-15</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1012,72 +971,70 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Tommy Tyrberg</t>
+          <t>Tomas Fasth</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Via Tommy Tyrberg</t>
-        </is>
-      </c>
-      <c r="AY4" t="inlineStr"/>
+          <t>Tomas Fasth</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>Ödeshög naturvårdsprogram uppdatering</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>87496105</v>
+        <v>69187279</v>
       </c>
       <c r="B5" t="n">
-        <v>101120</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79795</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>222002</v>
+        <v>374</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Underviol</t>
+          <t>Gul dropplav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Viola mirabilis</t>
+          <t>Cliostomum corrugatum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Ängsbacke V Sållerydsfuktängen, Ög</t>
+          <t>Sålleryd, Ög</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>491086.5284495048</v>
+        <v>491213</v>
       </c>
       <c r="R5" t="n">
-        <v>6458836.9344129</v>
+        <v>6458718</v>
       </c>
       <c r="S5" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1101,27 +1058,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>1975-06-07</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2017-11-15</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>1975-06-07</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Äldre uppgifter om Östergötlands flora. Referens: Hallberg, H. Peter 1975. Sektion 67, St Åby och Rök. Manuskript i PÖF Arkiv, Norrköping, 15+2 s. Inlagda i Artportalen av Tommy Tyrberg.</t>
+          <t>2017-11-15</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1136,27 +1078,26 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Tommy Tyrberg</t>
+          <t>Tomas Fasth</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Via Tommy Tyrberg</t>
-        </is>
-      </c>
-      <c r="AY5" t="inlineStr"/>
+          <t>Tomas Fasth</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>Ödeshög naturvårdsprogram uppdatering</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
         <v>96233395</v>
       </c>
       <c r="B6" t="n">
-        <v>89167</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91678</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1198,10 +1139,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>491132.6751575283</v>
+        <v>491133</v>
       </c>
       <c r="R6" t="n">
-        <v>6458970.431877468</v>
+        <v>6458970</v>
       </c>
       <c r="S6" t="n">
         <v>20</v>
@@ -1272,6 +1213,416 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>69187277</v>
+      </c>
+      <c r="B7" t="n">
+        <v>92244</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>721</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Korallticka</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Grifola frondosa</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Dicks.) Gray</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Sålleryd, Ög</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>491213</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6458718</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Ödeshög</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Rök</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2017-11-15</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2017-11-15</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Tomas Fasth</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Tomas Fasth</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>Ödeshög naturvårdsprogram uppdatering</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>69187280</v>
+      </c>
+      <c r="B8" t="n">
+        <v>75341</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>1114</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Gammelekslav</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Lecanographa amylacea</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Ehrh. ex Pers.) Egea &amp; Torrente</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Sålleryd, Ög</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>491243</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6458709</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Ödeshög</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Rök</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2017-11-15</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2017-11-15</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Tomas Fasth</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Tomas Fasth</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>Ödeshög naturvårdsprogram uppdatering</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>2454432</v>
+      </c>
+      <c r="B9" t="n">
+        <v>99022</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>220093</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Korallrot</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Corallorhiza trifida</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Châtel.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Sålleryd 150 m OSO, Ög</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>491414</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6458616</v>
+      </c>
+      <c r="S9" t="n">
+        <v>100</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Ödeshög</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Rök</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2002-07-20</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2002-07-20</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>Mossekant</t>
+        </is>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Jörgen Josefsson</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Jörgen Josefsson</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>6999611</v>
+      </c>
+      <c r="B10" t="n">
+        <v>106140</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>221137</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Majviva</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Primula farinosa</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Sålleryd, Ög</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>491186</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6458678</v>
+      </c>
+      <c r="S10" t="n">
+        <v>50</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Ödeshög</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Rök</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>1978-05-20</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>1999-10-07</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Medobservatör: Erik Genberg</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Stefan Karlsson</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Stefan Karlsson</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr">
+        <is>
+          <t>Äldre fynd i Östergötlands flora</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
